--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8444,0.2103,0.0056,0.0005</t>
-  </si>
-  <si>
-    <t>0.9830,0.0039,0.0045,0.0011</t>
-  </si>
-  <si>
-    <t>0.9470,0.0549,0.0025,0.0007</t>
-  </si>
-  <si>
-    <t>0.9361,0.0267,0.0074,0.0067</t>
-  </si>
-  <si>
-    <t>0.9923,0.0059,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9794,0.0142,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9523,0.0501,0.0026,0.0009</t>
-  </si>
-  <si>
-    <t>0.9380,0.0611,0.0037,0.0014</t>
-  </si>
-  <si>
-    <t>0.9511,0.0669,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.8462,0.2275,0.0025,0.0005</t>
-  </si>
-  <si>
-    <t>0.9625,0.0443,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9610,0.0397,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.9580,0.0216,0.0123,0.0001</t>
-  </si>
-  <si>
-    <t>0.8457,0.1031,0.0387,0.0024</t>
-  </si>
-  <si>
-    <t>0.9169,0.0178,0.0695,0.0002</t>
-  </si>
-  <si>
-    <t>0.8761,0.0244,0.1166,0.0013</t>
-  </si>
-  <si>
-    <t>0.8816,0.1133,0.0148,0.0012</t>
-  </si>
-  <si>
-    <t>0.9025,0.1448,0.0042,0.0002</t>
-  </si>
-  <si>
-    <t>0.8650,0.2067,0.0062,0.0001</t>
-  </si>
-  <si>
-    <t>0.9268,0.0859,0.0044,0.0004</t>
-  </si>
-  <si>
-    <t>0.7279,0.4748,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.9105,0.1464,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9874,0.0026,0.0068,0.0001</t>
-  </si>
-  <si>
-    <t>0.9902,0.0015,0.0080,0.0001</t>
-  </si>
-  <si>
-    <t>0.7911,0.0080,0.2686,0.0004</t>
-  </si>
-  <si>
-    <t>0.9875,0.0024,0.0094,0.0002</t>
-  </si>
-  <si>
-    <t>0.9012,0.0130,0.1159,0.0010</t>
-  </si>
-  <si>
-    <t>0.9451,0.0128,0.0456,0.0014</t>
-  </si>
-  <si>
-    <t>0.0503,0.0028,0.9768,0.0003</t>
-  </si>
-  <si>
-    <t>0.9702,0.0316,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.9434,0.0766,0.0030,0.0003</t>
-  </si>
-  <si>
-    <t>0.0251,0.1000,0.9494,0.0003</t>
-  </si>
-  <si>
-    <t>0.9120,0.1245,0.0049,0.0001</t>
-  </si>
-  <si>
-    <t>0.8750,0.1373,0.0047,0.0009</t>
-  </si>
-  <si>
-    <t>0.9569,0.0480,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.9495,0.0688,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9871,0.0137,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.6489,0.1814,0.0696,0.0008</t>
-  </si>
-  <si>
-    <t>0.9764,0.0003,0.0555,0.0001</t>
-  </si>
-  <si>
-    <t>0.9517,0.0047,0.0567,0.0004</t>
-  </si>
-  <si>
-    <t>0.9513,0.0017,0.0700,0.0023</t>
-  </si>
-  <si>
-    <t>0.9977,0.0001,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.2221,0.1141,0.1499,0.0000</t>
-  </si>
-  <si>
-    <t>0.9908,0.0014,0.0093,0.0002</t>
-  </si>
-  <si>
-    <t>0.9010,0.0892,0.0149,0.0023</t>
-  </si>
-  <si>
-    <t>0.9605,0.0340,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.8425,0.2279,0.0027,0.0000</t>
-  </si>
-  <si>
-    <t>0.9215,0.0691,0.0096,0.0003</t>
-  </si>
-  <si>
-    <t>0.0498,0.0045,0.9712,0.0011</t>
-  </si>
-  <si>
-    <t>0.7469,0.0076,0.3853,0.0004</t>
-  </si>
-  <si>
-    <t>0.9887,0.0018,0.0083,0.0002</t>
-  </si>
-  <si>
-    <t>0.9534,0.0038,0.0995,0.0006</t>
-  </si>
-  <si>
-    <t>0.5540,0.0055,0.6015,0.0006</t>
-  </si>
-  <si>
-    <t>0.6591,0.0443,0.1846,0.0005</t>
-  </si>
-  <si>
-    <t>0.9554,0.0520,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9296,0.0856,0.0030,0.0005</t>
-  </si>
-  <si>
-    <t>0.9535,0.0368,0.0017,0.0012</t>
-  </si>
-  <si>
-    <t>0.0473,0.8494,0.6292,0.0038</t>
-  </si>
-  <si>
-    <t>0.9515,0.0558,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9727,0.0283,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.7401,0.3550,0.0100,0.0006</t>
-  </si>
-  <si>
-    <t>0.0672,0.4566,0.9133,0.0013</t>
-  </si>
-  <si>
-    <t>0.5330,0.0131,0.6756,0.0002</t>
-  </si>
-  <si>
-    <t>0.6369,0.0276,0.4342,0.0006</t>
-  </si>
-  <si>
-    <t>0.2132,0.0940,0.7087,0.0002</t>
-  </si>
-  <si>
-    <t>0.6377,0.0042,0.6123,0.0003</t>
-  </si>
-  <si>
-    <t>0.9265,0.1242,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.2117,0.8777,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.9734,0.0260,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.8127,0.2676,0.0095,0.0003</t>
-  </si>
-  <si>
-    <t>0.0180,0.6846,0.9177,0.0012</t>
-  </si>
-  <si>
-    <t>0.7568,0.0286,0.2881,0.0001</t>
-  </si>
-  <si>
-    <t>0.9788,0.0065,0.0120,0.0001</t>
-  </si>
-  <si>
-    <t>0.4414,0.2639,0.0928,0.0001</t>
-  </si>
-  <si>
-    <t>0.2861,0.2850,0.3456,0.0002</t>
-  </si>
-  <si>
-    <t>0.8544,0.0505,0.1012,0.0076</t>
-  </si>
-  <si>
-    <t>0.9744,0.0081,0.0011,0.0034</t>
-  </si>
-  <si>
-    <t>0.9316,0.0306,0.0108,0.0048</t>
-  </si>
-  <si>
-    <t>0.9869,0.0055,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.9702,0.0087,0.0057,0.0039</t>
-  </si>
-  <si>
-    <t>0.9708,0.0107,0.0080,0.0016</t>
-  </si>
-  <si>
-    <t>0.5448,0.0738,0.4585,0.0006</t>
-  </si>
-  <si>
-    <t>0.3505,0.1761,0.2694,0.0004</t>
-  </si>
-  <si>
-    <t>0.6184,0.0039,0.6320,0.0005</t>
-  </si>
-  <si>
-    <t>0.9476,0.0106,0.0471,0.0002</t>
-  </si>
-  <si>
-    <t>0.9350,0.0367,0.0250,0.0003</t>
-  </si>
-  <si>
-    <t>0.8854,0.0244,0.0802,0.0004</t>
-  </si>
-  <si>
-    <t>0.8051,0.2751,0.0074,0.0007</t>
-  </si>
-  <si>
-    <t>0.9660,0.0364,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9263,0.0966,0.0033,0.0008</t>
-  </si>
-  <si>
-    <t>0.8734,0.1770,0.0034,0.0005</t>
-  </si>
-  <si>
-    <t>0.9577,0.0443,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.8223,0.2527,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.9499,0.0685,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9397,0.1020,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.9724,0.0303,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.8780,0.1761,0.0056,0.0008</t>
-  </si>
-  <si>
-    <t>0.8718,0.1463,0.0026,0.0008</t>
-  </si>
-  <si>
-    <t>0.9833,0.0145,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.8608,0.1643,0.0054,0.0012</t>
-  </si>
-  <si>
-    <t>0.8663,0.1763,0.0024,0.0010</t>
-  </si>
-  <si>
-    <t>0.9531,0.0507,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.9614,0.0413,0.0020,0.0009</t>
-  </si>
-  <si>
-    <t>0.0482,0.1132,0.9632,0.0005</t>
-  </si>
-  <si>
-    <t>0.5846,0.0286,0.4355,0.0010</t>
-  </si>
-  <si>
-    <t>0.9951,0.0007,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.9609,0.0146,0.0112,0.0006</t>
-  </si>
-  <si>
-    <t>0.3132,0.8083,0.0157,0.0004</t>
-  </si>
-  <si>
-    <t>0.1908,0.8793,0.0160,0.0010</t>
-  </si>
-  <si>
-    <t>0.8203,0.3388,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.9394,0.0648,0.0026,0.0008</t>
-  </si>
-  <si>
-    <t>0.7465,0.3681,0.0079,0.0004</t>
-  </si>
-  <si>
-    <t>0.5692,0.6376,0.0045,0.0004</t>
-  </si>
-  <si>
-    <t>0.3324,0.7937,0.0175,0.0013</t>
-  </si>
-  <si>
-    <t>0.8155,0.2540,0.0178,0.0005</t>
-  </si>
-  <si>
-    <t>0.8242,0.0209,0.1808,0.0010</t>
-  </si>
-  <si>
-    <t>0.9893,0.0022,0.0050,0.0003</t>
-  </si>
-  <si>
-    <t>0.9774,0.0103,0.0054,0.0002</t>
-  </si>
-  <si>
-    <t>0.8698,0.1069,0.0179,0.0040</t>
-  </si>
-  <si>
-    <t>0.9388,0.1098,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.9439,0.0866,0.0040,0.0002</t>
-  </si>
-  <si>
-    <t>0.9378,0.0439,0.0080,0.0005</t>
-  </si>
-  <si>
-    <t>0.3412,0.2099,0.1066,0.0001</t>
-  </si>
-  <si>
-    <t>0.7915,0.2629,0.0153,0.0004</t>
-  </si>
-  <si>
-    <t>0.9212,0.0933,0.0044,0.0006</t>
-  </si>
-  <si>
-    <t>0.9601,0.0489,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9791,0.0268,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9681,0.0250,0.0011,0.0008</t>
-  </si>
-  <si>
-    <t>0.9161,0.1168,0.0038,0.0004</t>
-  </si>
-  <si>
-    <t>0.9208,0.0950,0.0035,0.0005</t>
-  </si>
-  <si>
-    <t>0.8797,0.1732,0.0044,0.0005</t>
-  </si>
-  <si>
-    <t>0.8829,0.1774,0.0043,0.0003</t>
-  </si>
-  <si>
-    <t>0.9600,0.0374,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9618,0.0394,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9635,0.0016,0.0584,0.0002</t>
-  </si>
-  <si>
-    <t>0.8975,0.0073,0.1712,0.0002</t>
-  </si>
-  <si>
-    <t>0.9524,0.0033,0.0560,0.0001</t>
-  </si>
-  <si>
-    <t>0.9727,0.0005,0.0827,0.0000</t>
-  </si>
-  <si>
-    <t>0.9899,0.0027,0.0040,0.0002</t>
-  </si>
-  <si>
-    <t>0.7975,0.1397,0.0426,0.0013</t>
-  </si>
-  <si>
-    <t>0.9400,0.0203,0.0420,0.0005</t>
-  </si>
-  <si>
-    <t>0.9921,0.0031,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9870,0.0025,0.0013,0.0014</t>
-  </si>
-  <si>
-    <t>0.5189,0.0211,0.1023,0.4267</t>
-  </si>
-  <si>
-    <t>0.9538,0.0180,0.0080,0.0044</t>
-  </si>
-  <si>
-    <t>0.9632,0.0078,0.0059,0.0072</t>
-  </si>
-  <si>
-    <t>0.2390,0.6610,0.0818,0.0002</t>
-  </si>
-  <si>
-    <t>0.9615,0.0506,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9348,0.0620,0.0091,0.0004</t>
-  </si>
-  <si>
-    <t>0.9360,0.1092,0.0021,0.0002</t>
-  </si>
-  <si>
-    <t>0.9677,0.0324,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.6711,0.5023,0.0077,0.0007</t>
-  </si>
-  <si>
-    <t>0.9148,0.0753,0.0122,0.0020</t>
-  </si>
-  <si>
-    <t>0.9107,0.0892,0.0030,0.0011</t>
-  </si>
-  <si>
-    <t>0.0897,0.3033,0.8270,0.0087</t>
-  </si>
-  <si>
-    <t>0.9343,0.0542,0.0067,0.0014</t>
-  </si>
-  <si>
-    <t>0.6483,0.3251,0.0720,0.0095</t>
-  </si>
-  <si>
-    <t>0.9881,0.0090,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9610,0.0459,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.9265,0.0929,0.0050,0.0004</t>
-  </si>
-  <si>
-    <t>0.9701,0.0245,0.0021,0.0002</t>
-  </si>
-  <si>
-    <t>0.9746,0.0262,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9284,0.1318,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.7862,0.2281,0.0154,0.0026</t>
-  </si>
-  <si>
-    <t>0.9438,0.0457,0.0017,0.0015</t>
-  </si>
-  <si>
-    <t>0.7277,0.4071,0.0054,0.0008</t>
-  </si>
-  <si>
-    <t>0.9547,0.0522,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.9751,0.0255,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9642,0.0242,0.0022,0.0015</t>
-  </si>
-  <si>
-    <t>0.9240,0.0680,0.0033,0.0013</t>
-  </si>
-  <si>
-    <t>0.9545,0.0498,0.0021,0.0011</t>
-  </si>
-  <si>
-    <t>0.9595,0.0461,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.8868,0.1568,0.0050,0.0006</t>
-  </si>
-  <si>
-    <t>0.9472,0.0792,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.4197,0.4804,0.1301,0.0018</t>
-  </si>
-  <si>
-    <t>0.9720,0.0316,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.8538,0.2443,0.0038,0.0004</t>
-  </si>
-  <si>
-    <t>0.9297,0.0672,0.0025,0.0009</t>
-  </si>
-  <si>
-    <t>0.9837,0.0173,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.0022,0.6464,0.9919,0.0003</t>
-  </si>
-  <si>
-    <t>0.9263,0.0938,0.0039,0.0008</t>
-  </si>
-  <si>
-    <t>0.5247,0.0064,0.6057,0.0003</t>
-  </si>
-  <si>
-    <t>0.6658,0.0080,0.5393,0.0008</t>
-  </si>
-  <si>
-    <t>0.9851,0.0070,0.0052,0.0001</t>
-  </si>
-  <si>
-    <t>0.6051,0.0323,0.3507,0.0001</t>
-  </si>
-  <si>
-    <t>0.2064,0.0357,0.8180,0.0007</t>
-  </si>
-  <si>
-    <t>0.6903,0.0192,0.4248,0.0013</t>
-  </si>
-  <si>
-    <t>0.6146,0.0789,0.2413,0.0006</t>
-  </si>
-  <si>
-    <t>0.9842,0.0051,0.0052,0.0002</t>
-  </si>
-  <si>
-    <t>0.9788,0.0060,0.0114,0.0003</t>
-  </si>
-  <si>
-    <t>0.9773,0.0108,0.0052,0.0004</t>
-  </si>
-  <si>
-    <t>0.9671,0.0234,0.0058,0.0002</t>
-  </si>
-  <si>
-    <t>0.9900,0.0090,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9108,0.0627,0.0150,0.0002</t>
-  </si>
-  <si>
-    <t>0.9750,0.0148,0.0042,0.0003</t>
-  </si>
-  <si>
-    <t>0.9282,0.0638,0.0147,0.0005</t>
-  </si>
-  <si>
-    <t>0.7839,0.3568,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.9434,0.0772,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.8384,0.3262,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.9543,0.0584,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.7494,0.4341,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.9858,0.0043,0.0057,0.0002</t>
-  </si>
-  <si>
-    <t>0.9777,0.0095,0.0061,0.0003</t>
-  </si>
-  <si>
-    <t>0.9750,0.0078,0.0128,0.0002</t>
-  </si>
-  <si>
-    <t>0.9738,0.0073,0.0178,0.0006</t>
-  </si>
-  <si>
-    <t>0.8825,0.0180,0.1294,0.0018</t>
-  </si>
-  <si>
-    <t>0.4469,0.0619,0.5039,0.0009</t>
-  </si>
-  <si>
-    <t>0.8663,0.0317,0.1228,0.0025</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.9940,0.0005,0.0059,0.0000</t>
-  </si>
-  <si>
-    <t>0.9501,0.0081,0.0501,0.0004</t>
-  </si>
-  <si>
-    <t>0.9588,0.0293,0.0037,0.0016</t>
-  </si>
-  <si>
-    <t>0.9493,0.0530,0.0035,0.0007</t>
-  </si>
-  <si>
-    <t>0.9571,0.0363,0.0018,0.0007</t>
-  </si>
-  <si>
-    <t>0.9601,0.0479,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9103,0.1194,0.0034,0.0005</t>
-  </si>
-  <si>
-    <t>0.9408,0.0582,0.0036,0.0011</t>
-  </si>
-  <si>
-    <t>0.9341,0.0807,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.9573,0.0512,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9157,0.0566,0.0339,0.0010</t>
-  </si>
-  <si>
-    <t>0.8518,0.1480,0.0190,0.0013</t>
-  </si>
-  <si>
-    <t>0.9360,0.0643,0.0063,0.0011</t>
-  </si>
-  <si>
-    <t>0.5550,0.0231,0.5453,0.0002</t>
-  </si>
-  <si>
-    <t>0.2017,0.0173,0.8170,0.0016</t>
-  </si>
-  <si>
-    <t>0.8671,0.0068,0.2090,0.0003</t>
-  </si>
-  <si>
-    <t>0.0617,0.0919,0.9493,0.0006</t>
-  </si>
-  <si>
-    <t>0.8245,0.0025,0.3646,0.0005</t>
-  </si>
-  <si>
-    <t>0.0619,0.0164,0.9498,0.0005</t>
-  </si>
-  <si>
-    <t>0.9049,0.0019,0.2230,0.0005</t>
-  </si>
-  <si>
-    <t>0.9833,0.0058,0.0052,0.0001</t>
-  </si>
-  <si>
-    <t>0.9895,0.0022,0.0038,0.0004</t>
-  </si>
-  <si>
-    <t>0.9942,0.0011,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.9758,0.0135,0.0043,0.0004</t>
-  </si>
-  <si>
-    <t>0.9645,0.0530,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.8167,0.2665,0.0090,0.0008</t>
-  </si>
-  <si>
-    <t>0.9726,0.0253,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.8829,0.2135,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.9163,0.1279,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.9059,0.1287,0.0048,0.0013</t>
-  </si>
-  <si>
-    <t>0.8683,0.1743,0.0043,0.0010</t>
-  </si>
-  <si>
-    <t>0.7163,0.3439,0.0102,0.0019</t>
-  </si>
-  <si>
-    <t>0.9937,0.0009,0.0051,0.0001</t>
-  </si>
-  <si>
-    <t>0.2036,0.0053,0.9156,0.0003</t>
-  </si>
-  <si>
-    <t>0.8851,0.0147,0.1065,0.0005</t>
-  </si>
-  <si>
-    <t>0.9549,0.0076,0.0351,0.0003</t>
-  </si>
-  <si>
-    <t>0.9715,0.0008,0.0641,0.0001</t>
-  </si>
-  <si>
-    <t>0.9797,0.0070,0.0083,0.0002</t>
-  </si>
-  <si>
-    <t>0.9365,0.0118,0.0368,0.0002</t>
-  </si>
-  <si>
-    <t>0.9440,0.0022,0.1067,0.0004</t>
-  </si>
-  <si>
-    <t>0.8728,0.0882,0.0351,0.0056</t>
-  </si>
-  <si>
-    <t>0.8951,0.0180,0.0794,0.0108</t>
-  </si>
-  <si>
-    <t>0.9741,0.0063,0.0050,0.0031</t>
-  </si>
-  <si>
-    <t>0.9014,0.0686,0.0190,0.0052</t>
-  </si>
-  <si>
-    <t>0.9098,0.0359,0.0171,0.0159</t>
-  </si>
-  <si>
-    <t>0.9554,0.0407,0.0062,0.0004</t>
+    <t>0.9717,0.0141,0.0063,0.0006</t>
+  </si>
+  <si>
+    <t>0.7975,0.1192,0.0440,0.0136</t>
+  </si>
+  <si>
+    <t>0.8249,0.1934,0.0153,0.0016</t>
+  </si>
+  <si>
+    <t>0.9779,0.0070,0.0033,0.0017</t>
+  </si>
+  <si>
+    <t>0.9816,0.0114,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9676,0.0359,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9707,0.0378,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9107,0.1157,0.0032,0.0011</t>
+  </si>
+  <si>
+    <t>0.9651,0.0405,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.9127,0.1033,0.0032,0.0008</t>
+  </si>
+  <si>
+    <t>0.9818,0.0130,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9953,0.0027,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9865,0.0054,0.0048,0.0001</t>
+  </si>
+  <si>
+    <t>0.9139,0.0423,0.0397,0.0009</t>
+  </si>
+  <si>
+    <t>0.9781,0.0058,0.0132,0.0003</t>
+  </si>
+  <si>
+    <t>0.9781,0.0036,0.0206,0.0003</t>
+  </si>
+  <si>
+    <t>0.9255,0.0848,0.0070,0.0003</t>
+  </si>
+  <si>
+    <t>0.7630,0.4418,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.5474,0.6006,0.0137,0.0004</t>
+  </si>
+  <si>
+    <t>0.9810,0.0192,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.0261,0.9837,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.6429,0.5309,0.0082,0.0002</t>
+  </si>
+  <si>
+    <t>0.9913,0.0018,0.0042,0.0001</t>
+  </si>
+  <si>
+    <t>0.9910,0.0007,0.0114,0.0001</t>
+  </si>
+  <si>
+    <t>0.9817,0.0013,0.0206,0.0005</t>
+  </si>
+  <si>
+    <t>0.9832,0.0026,0.0158,0.0002</t>
+  </si>
+  <si>
+    <t>0.9689,0.0045,0.0365,0.0002</t>
+  </si>
+  <si>
+    <t>0.9627,0.0065,0.0385,0.0008</t>
+  </si>
+  <si>
+    <t>0.8561,0.0022,0.2863,0.0006</t>
+  </si>
+  <si>
+    <t>0.9211,0.0983,0.0047,0.0001</t>
+  </si>
+  <si>
+    <t>0.9867,0.0115,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0064,0.7130,0.9766,0.0003</t>
+  </si>
+  <si>
+    <t>0.7457,0.2705,0.0225,0.0002</t>
+  </si>
+  <si>
+    <t>0.8409,0.1828,0.0145,0.0012</t>
+  </si>
+  <si>
+    <t>0.9182,0.0711,0.0143,0.0015</t>
+  </si>
+  <si>
+    <t>0.9858,0.0104,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9928,0.0048,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.7227,0.0195,0.4725,0.0006</t>
+  </si>
+  <si>
+    <t>0.9817,0.0004,0.0488,0.0001</t>
+  </si>
+  <si>
+    <t>0.9720,0.0014,0.0550,0.0001</t>
+  </si>
+  <si>
+    <t>0.9956,0.0003,0.0047,0.0001</t>
+  </si>
+  <si>
+    <t>0.9645,0.0122,0.0163,0.0001</t>
+  </si>
+  <si>
+    <t>0.2388,0.0709,0.3591,0.0003</t>
+  </si>
+  <si>
+    <t>0.9781,0.0033,0.0228,0.0002</t>
+  </si>
+  <si>
+    <t>0.9857,0.0104,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9784,0.0264,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.4255,0.5091,0.0174,0.0000</t>
+  </si>
+  <si>
+    <t>0.9780,0.0262,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0943,0.1749,0.8150,0.0011</t>
+  </si>
+  <si>
+    <t>0.7273,0.0043,0.4723,0.0006</t>
+  </si>
+  <si>
+    <t>0.9745,0.0033,0.0262,0.0002</t>
+  </si>
+  <si>
+    <t>0.6752,0.0136,0.3409,0.0003</t>
+  </si>
+  <si>
+    <t>0.4490,0.0172,0.6356,0.0002</t>
+  </si>
+  <si>
+    <t>0.9232,0.0203,0.0532,0.0003</t>
+  </si>
+  <si>
+    <t>0.9198,0.0917,0.0060,0.0003</t>
+  </si>
+  <si>
+    <t>0.9354,0.0505,0.0026,0.0015</t>
+  </si>
+  <si>
+    <t>0.8760,0.1272,0.0033,0.0011</t>
+  </si>
+  <si>
+    <t>0.3047,0.3898,0.3931,0.0023</t>
+  </si>
+  <si>
+    <t>0.9848,0.0090,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9931,0.0048,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9656,0.0474,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.8081,0.0170,0.2665,0.0004</t>
+  </si>
+  <si>
+    <t>0.2923,0.0087,0.8686,0.0003</t>
+  </si>
+  <si>
+    <t>0.8833,0.0076,0.2225,0.0012</t>
+  </si>
+  <si>
+    <t>0.1101,0.3982,0.6678,0.0002</t>
+  </si>
+  <si>
+    <t>0.4065,0.0099,0.7863,0.0005</t>
+  </si>
+  <si>
+    <t>0.9451,0.0902,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.2332,0.8702,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.9877,0.0083,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.9732,0.0363,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.4230,0.2089,0.2068,0.0005</t>
+  </si>
+  <si>
+    <t>0.7990,0.0349,0.1652,0.0005</t>
+  </si>
+  <si>
+    <t>0.9562,0.0122,0.0272,0.0001</t>
+  </si>
+  <si>
+    <t>0.4431,0.3792,0.0304,0.0001</t>
+  </si>
+  <si>
+    <t>0.2177,0.0899,0.7092,0.0001</t>
+  </si>
+  <si>
+    <t>0.9677,0.0096,0.0120,0.0020</t>
+  </si>
+  <si>
+    <t>0.9789,0.0071,0.0009,0.0017</t>
+  </si>
+  <si>
+    <t>0.9665,0.0101,0.0042,0.0041</t>
+  </si>
+  <si>
+    <t>0.9381,0.0226,0.0113,0.0058</t>
+  </si>
+  <si>
+    <t>0.9105,0.0601,0.0181,0.0040</t>
+  </si>
+  <si>
+    <t>0.9213,0.0711,0.0097,0.0007</t>
+  </si>
+  <si>
+    <t>0.6799,0.1101,0.2210,0.0009</t>
+  </si>
+  <si>
+    <t>0.7142,0.0058,0.4002,0.0002</t>
+  </si>
+  <si>
+    <t>0.5653,0.0308,0.3819,0.0009</t>
+  </si>
+  <si>
+    <t>0.7425,0.0080,0.4953,0.0002</t>
+  </si>
+  <si>
+    <t>0.9134,0.0202,0.0631,0.0002</t>
+  </si>
+  <si>
+    <t>0.8972,0.0261,0.0269,0.0000</t>
+  </si>
+  <si>
+    <t>0.9317,0.0643,0.0030,0.0013</t>
+  </si>
+  <si>
+    <t>0.9086,0.1296,0.0033,0.0005</t>
+  </si>
+  <si>
+    <t>0.9288,0.0704,0.0041,0.0013</t>
+  </si>
+  <si>
+    <t>0.8524,0.1834,0.0148,0.0009</t>
+  </si>
+  <si>
+    <t>0.9862,0.0130,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.8934,0.1371,0.0043,0.0008</t>
+  </si>
+  <si>
+    <t>0.9629,0.0501,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.6118,0.5112,0.0118,0.0011</t>
+  </si>
+  <si>
+    <t>0.9657,0.0328,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9609,0.0402,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.9520,0.0472,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9672,0.0398,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9664,0.0374,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9773,0.0226,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9740,0.0349,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.8179,0.2234,0.0085,0.0019</t>
+  </si>
+  <si>
+    <t>0.0921,0.0273,0.9410,0.0003</t>
+  </si>
+  <si>
+    <t>0.9814,0.0016,0.0251,0.0002</t>
+  </si>
+  <si>
+    <t>0.9535,0.0115,0.0354,0.0006</t>
+  </si>
+  <si>
+    <t>0.9762,0.0048,0.0156,0.0006</t>
+  </si>
+  <si>
+    <t>0.7820,0.3435,0.0051,0.0003</t>
+  </si>
+  <si>
+    <t>0.8333,0.2793,0.0053,0.0002</t>
+  </si>
+  <si>
+    <t>0.7737,0.4024,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.6837,0.4865,0.0136,0.0004</t>
+  </si>
+  <si>
+    <t>0.6582,0.5379,0.0044,0.0002</t>
+  </si>
+  <si>
+    <t>0.0387,0.9719,0.0140,0.0001</t>
+  </si>
+  <si>
+    <t>0.9119,0.1280,0.0063,0.0009</t>
+  </si>
+  <si>
+    <t>0.9668,0.0323,0.0023,0.0002</t>
+  </si>
+  <si>
+    <t>0.9830,0.0046,0.0119,0.0002</t>
+  </si>
+  <si>
+    <t>0.9851,0.0037,0.0062,0.0002</t>
+  </si>
+  <si>
+    <t>0.8829,0.0499,0.0653,0.0025</t>
+  </si>
+  <si>
+    <t>0.9831,0.0062,0.0045,0.0002</t>
+  </si>
+  <si>
+    <t>0.9900,0.0080,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.9481,0.0922,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.8905,0.1528,0.0054,0.0001</t>
+  </si>
+  <si>
+    <t>0.5804,0.0271,0.2284,0.0002</t>
+  </si>
+  <si>
+    <t>0.8539,0.1852,0.0061,0.0001</t>
+  </si>
+  <si>
+    <t>0.8795,0.1743,0.0049,0.0005</t>
+  </si>
+  <si>
+    <t>0.8365,0.2378,0.0109,0.0007</t>
+  </si>
+  <si>
+    <t>0.9307,0.0945,0.0042,0.0005</t>
+  </si>
+  <si>
+    <t>0.9349,0.0686,0.0020,0.0012</t>
+  </si>
+  <si>
+    <t>0.9254,0.0862,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.8400,0.1974,0.0082,0.0006</t>
+  </si>
+  <si>
+    <t>0.9742,0.0217,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9742,0.0243,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.8597,0.1991,0.0062,0.0005</t>
+  </si>
+  <si>
+    <t>0.8476,0.1696,0.0125,0.0016</t>
+  </si>
+  <si>
+    <t>0.9894,0.0005,0.0212,0.0001</t>
+  </si>
+  <si>
+    <t>0.9289,0.0122,0.0719,0.0003</t>
+  </si>
+  <si>
+    <t>0.4417,0.0143,0.5341,0.0003</t>
+  </si>
+  <si>
+    <t>0.9583,0.0010,0.0864,0.0001</t>
+  </si>
+  <si>
+    <t>0.9662,0.0350,0.0038,0.0002</t>
+  </si>
+  <si>
+    <t>0.9754,0.0143,0.0030,0.0002</t>
+  </si>
+  <si>
+    <t>0.9372,0.0270,0.0312,0.0006</t>
+  </si>
+  <si>
+    <t>0.9882,0.0036,0.0052,0.0001</t>
+  </si>
+  <si>
+    <t>0.9940,0.0016,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.7936,0.0375,0.0717,0.0639</t>
+  </si>
+  <si>
+    <t>0.9346,0.0097,0.0365,0.0074</t>
+  </si>
+  <si>
+    <t>0.9840,0.0018,0.0016,0.0050</t>
+  </si>
+  <si>
+    <t>0.8934,0.0447,0.0347,0.0003</t>
+  </si>
+  <si>
+    <t>0.9657,0.0256,0.0012,0.0009</t>
+  </si>
+  <si>
+    <t>0.8007,0.2653,0.0085,0.0006</t>
+  </si>
+  <si>
+    <t>0.9513,0.0701,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9332,0.0837,0.0040,0.0004</t>
+  </si>
+  <si>
+    <t>0.9096,0.1178,0.0051,0.0004</t>
+  </si>
+  <si>
+    <t>0.9524,0.0373,0.0063,0.0008</t>
+  </si>
+  <si>
+    <t>0.9214,0.0806,0.0028,0.0009</t>
+  </si>
+  <si>
+    <t>0.5446,0.2046,0.3156,0.0024</t>
+  </si>
+  <si>
+    <t>0.9134,0.0850,0.0083,0.0009</t>
+  </si>
+  <si>
+    <t>0.7864,0.1859,0.0142,0.0051</t>
+  </si>
+  <si>
+    <t>0.8464,0.2126,0.0066,0.0007</t>
+  </si>
+  <si>
+    <t>0.9790,0.0231,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9794,0.0233,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.8154,0.2734,0.0102,0.0002</t>
+  </si>
+  <si>
+    <t>0.9705,0.0302,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.9886,0.0142,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9834,0.0226,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9905,0.0087,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9737,0.0214,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.6874,0.4076,0.0141,0.0018</t>
+  </si>
+  <si>
+    <t>0.9679,0.0189,0.0019,0.0017</t>
+  </si>
+  <si>
+    <t>0.7812,0.3296,0.0057,0.0008</t>
+  </si>
+  <si>
+    <t>0.9707,0.0289,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9345,0.0788,0.0029,0.0007</t>
+  </si>
+  <si>
+    <t>0.9848,0.0119,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.7119,0.4171,0.0116,0.0010</t>
+  </si>
+  <si>
+    <t>0.8718,0.1255,0.0193,0.0012</t>
+  </si>
+  <si>
+    <t>0.5002,0.3201,0.3102,0.0053</t>
+  </si>
+  <si>
+    <t>0.7162,0.4292,0.0094,0.0006</t>
+  </si>
+  <si>
+    <t>0.9803,0.0203,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.6862,0.5180,0.0056,0.0004</t>
+  </si>
+  <si>
+    <t>0.9892,0.0106,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0482,0.2687,0.9363,0.0023</t>
+  </si>
+  <si>
+    <t>0.8835,0.1604,0.0086,0.0005</t>
+  </si>
+  <si>
+    <t>0.8305,0.0058,0.2838,0.0007</t>
+  </si>
+  <si>
+    <t>0.9481,0.0087,0.0563,0.0006</t>
+  </si>
+  <si>
+    <t>0.9748,0.0052,0.0215,0.0007</t>
+  </si>
+  <si>
+    <t>0.1627,0.0207,0.9076,0.0001</t>
+  </si>
+  <si>
+    <t>0.4905,0.0080,0.6360,0.0010</t>
+  </si>
+  <si>
+    <t>0.9294,0.0015,0.1571,0.0002</t>
+  </si>
+  <si>
+    <t>0.9744,0.0076,0.0186,0.0004</t>
+  </si>
+  <si>
+    <t>0.9736,0.0072,0.0204,0.0002</t>
+  </si>
+  <si>
+    <t>0.9825,0.0053,0.0096,0.0002</t>
+  </si>
+  <si>
+    <t>0.9319,0.0511,0.0148,0.0004</t>
+  </si>
+  <si>
+    <t>0.9571,0.0304,0.0090,0.0001</t>
+  </si>
+  <si>
+    <t>0.9475,0.0158,0.0187,0.0011</t>
+  </si>
+  <si>
+    <t>0.9481,0.0310,0.0115,0.0003</t>
+  </si>
+  <si>
+    <t>0.9742,0.0069,0.0223,0.0003</t>
+  </si>
+  <si>
+    <t>0.9543,0.0151,0.0255,0.0006</t>
+  </si>
+  <si>
+    <t>0.9867,0.0125,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9132,0.1581,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.8996,0.2341,0.0025,0.0002</t>
+  </si>
+  <si>
+    <t>0.9574,0.0452,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9799,0.0159,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9930,0.0015,0.0036,0.0001</t>
+  </si>
+  <si>
+    <t>0.9511,0.0245,0.0138,0.0002</t>
+  </si>
+  <si>
+    <t>0.9837,0.0019,0.0108,0.0005</t>
+  </si>
+  <si>
+    <t>0.9837,0.0072,0.0049,0.0002</t>
+  </si>
+  <si>
+    <t>0.9598,0.0203,0.0115,0.0008</t>
+  </si>
+  <si>
+    <t>0.7138,0.0955,0.1601,0.0009</t>
+  </si>
+  <si>
+    <t>0.9862,0.0009,0.0202,0.0001</t>
+  </si>
+  <si>
+    <t>0.9755,0.0025,0.0243,0.0004</t>
+  </si>
+  <si>
+    <t>0.9929,0.0006,0.0110,0.0001</t>
+  </si>
+  <si>
+    <t>0.9465,0.0012,0.1372,0.0001</t>
+  </si>
+  <si>
+    <t>0.9136,0.1076,0.0032,0.0006</t>
+  </si>
+  <si>
+    <t>0.9566,0.0328,0.0016,0.0012</t>
+  </si>
+  <si>
+    <t>0.9509,0.0556,0.0020,0.0008</t>
+  </si>
+  <si>
+    <t>0.8852,0.1281,0.0111,0.0017</t>
+  </si>
+  <si>
+    <t>0.9747,0.0183,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.8894,0.1728,0.0052,0.0004</t>
+  </si>
+  <si>
+    <t>0.9857,0.0107,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.8610,0.1301,0.0061,0.0023</t>
+  </si>
+  <si>
+    <t>0.6440,0.0449,0.2468,0.0004</t>
+  </si>
+  <si>
+    <t>0.9828,0.0075,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.9744,0.0241,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.3087,0.0126,0.8312,0.0003</t>
+  </si>
+  <si>
+    <t>0.0094,0.0057,0.9931,0.0003</t>
+  </si>
+  <si>
+    <t>0.9471,0.0142,0.0473,0.0004</t>
+  </si>
+  <si>
+    <t>0.2592,0.0037,0.8888,0.0005</t>
+  </si>
+  <si>
+    <t>0.6367,0.2351,0.0250,0.0003</t>
+  </si>
+  <si>
+    <t>0.0097,0.0148,0.9835,0.0019</t>
+  </si>
+  <si>
+    <t>0.9751,0.0016,0.0535,0.0003</t>
+  </si>
+  <si>
+    <t>0.9363,0.0215,0.0285,0.0004</t>
+  </si>
+  <si>
+    <t>0.9879,0.0026,0.0068,0.0003</t>
+  </si>
+  <si>
+    <t>0.9810,0.0038,0.0135,0.0003</t>
+  </si>
+  <si>
+    <t>0.9590,0.0144,0.0184,0.0005</t>
+  </si>
+  <si>
+    <t>0.7800,0.3530,0.0060,0.0005</t>
+  </si>
+  <si>
+    <t>0.8914,0.1213,0.0044,0.0014</t>
+  </si>
+  <si>
+    <t>0.9636,0.0341,0.0016,0.0010</t>
+  </si>
+  <si>
+    <t>0.9501,0.0635,0.0024,0.0007</t>
+  </si>
+  <si>
+    <t>0.9802,0.0196,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9657,0.0333,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.9630,0.0384,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9354,0.0524,0.0027,0.0017</t>
+  </si>
+  <si>
+    <t>0.9510,0.0056,0.0590,0.0002</t>
+  </si>
+  <si>
+    <t>0.8250,0.0031,0.3462,0.0007</t>
+  </si>
+  <si>
+    <t>0.1046,0.0238,0.8837,0.0033</t>
+  </si>
+  <si>
+    <t>0.9780,0.0034,0.0241,0.0003</t>
+  </si>
+  <si>
+    <t>0.8426,0.0042,0.2334,0.0002</t>
+  </si>
+  <si>
+    <t>0.8354,0.0133,0.2111,0.0009</t>
+  </si>
+  <si>
+    <t>0.7953,0.0140,0.2902,0.0014</t>
+  </si>
+  <si>
+    <t>0.9099,0.0084,0.0886,0.0008</t>
+  </si>
+  <si>
+    <t>0.9913,0.0023,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9506,0.0232,0.0132,0.0019</t>
+  </si>
+  <si>
+    <t>0.9842,0.0031,0.0035,0.0018</t>
+  </si>
+  <si>
+    <t>0.9650,0.0138,0.0045,0.0040</t>
+  </si>
+  <si>
+    <t>0.9593,0.0085,0.0047,0.0074</t>
+  </si>
+  <si>
+    <t>0.9802,0.0156,0.0018,0.0002</t>
   </si>
 </sst>
 </file>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2387,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D33" t="s">
         <v>295</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3269,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D96" t="s">
         <v>358</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4067,7 +4067,7 @@
         <v>259</v>
       </c>
       <c r="C153" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D153" t="s">
         <v>415</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4431,7 +4431,7 @@
         <v>259</v>
       </c>
       <c r="C179" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D179" t="s">
         <v>441</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9717,0.0141,0.0063,0.0006</t>
-  </si>
-  <si>
-    <t>0.7975,0.1192,0.0440,0.0136</t>
-  </si>
-  <si>
-    <t>0.8249,0.1934,0.0153,0.0016</t>
-  </si>
-  <si>
-    <t>0.9779,0.0070,0.0033,0.0017</t>
-  </si>
-  <si>
-    <t>0.9816,0.0114,0.0011,0.0007</t>
-  </si>
-  <si>
-    <t>0.9676,0.0359,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9707,0.0378,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9107,0.1157,0.0032,0.0011</t>
-  </si>
-  <si>
-    <t>0.9651,0.0405,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.9127,0.1033,0.0032,0.0008</t>
-  </si>
-  <si>
-    <t>0.9818,0.0130,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9953,0.0027,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9865,0.0054,0.0048,0.0001</t>
-  </si>
-  <si>
-    <t>0.9139,0.0423,0.0397,0.0009</t>
-  </si>
-  <si>
-    <t>0.9781,0.0058,0.0132,0.0003</t>
-  </si>
-  <si>
-    <t>0.9781,0.0036,0.0206,0.0003</t>
-  </si>
-  <si>
-    <t>0.9255,0.0848,0.0070,0.0003</t>
-  </si>
-  <si>
-    <t>0.7630,0.4418,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.5474,0.6006,0.0137,0.0004</t>
-  </si>
-  <si>
-    <t>0.9810,0.0192,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.0261,0.9837,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.6429,0.5309,0.0082,0.0002</t>
-  </si>
-  <si>
-    <t>0.9913,0.0018,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.9910,0.0007,0.0114,0.0001</t>
-  </si>
-  <si>
-    <t>0.9817,0.0013,0.0206,0.0005</t>
-  </si>
-  <si>
-    <t>0.9832,0.0026,0.0158,0.0002</t>
-  </si>
-  <si>
-    <t>0.9689,0.0045,0.0365,0.0002</t>
-  </si>
-  <si>
-    <t>0.9627,0.0065,0.0385,0.0008</t>
-  </si>
-  <si>
-    <t>0.8561,0.0022,0.2863,0.0006</t>
-  </si>
-  <si>
-    <t>0.9211,0.0983,0.0047,0.0001</t>
-  </si>
-  <si>
-    <t>0.9867,0.0115,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0064,0.7130,0.9766,0.0003</t>
-  </si>
-  <si>
-    <t>0.7457,0.2705,0.0225,0.0002</t>
-  </si>
-  <si>
-    <t>0.8409,0.1828,0.0145,0.0012</t>
-  </si>
-  <si>
-    <t>0.9182,0.0711,0.0143,0.0015</t>
-  </si>
-  <si>
-    <t>0.9858,0.0104,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9928,0.0048,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.7227,0.0195,0.4725,0.0006</t>
-  </si>
-  <si>
-    <t>0.9817,0.0004,0.0488,0.0001</t>
-  </si>
-  <si>
-    <t>0.9720,0.0014,0.0550,0.0001</t>
-  </si>
-  <si>
-    <t>0.9956,0.0003,0.0047,0.0001</t>
-  </si>
-  <si>
-    <t>0.9645,0.0122,0.0163,0.0001</t>
-  </si>
-  <si>
-    <t>0.2388,0.0709,0.3591,0.0003</t>
-  </si>
-  <si>
-    <t>0.9781,0.0033,0.0228,0.0002</t>
-  </si>
-  <si>
-    <t>0.9857,0.0104,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9784,0.0264,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.4255,0.5091,0.0174,0.0000</t>
-  </si>
-  <si>
-    <t>0.9780,0.0262,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0943,0.1749,0.8150,0.0011</t>
-  </si>
-  <si>
-    <t>0.7273,0.0043,0.4723,0.0006</t>
-  </si>
-  <si>
-    <t>0.9745,0.0033,0.0262,0.0002</t>
-  </si>
-  <si>
-    <t>0.6752,0.0136,0.3409,0.0003</t>
-  </si>
-  <si>
-    <t>0.4490,0.0172,0.6356,0.0002</t>
-  </si>
-  <si>
-    <t>0.9232,0.0203,0.0532,0.0003</t>
-  </si>
-  <si>
-    <t>0.9198,0.0917,0.0060,0.0003</t>
-  </si>
-  <si>
-    <t>0.9354,0.0505,0.0026,0.0015</t>
-  </si>
-  <si>
-    <t>0.8760,0.1272,0.0033,0.0011</t>
-  </si>
-  <si>
-    <t>0.3047,0.3898,0.3931,0.0023</t>
-  </si>
-  <si>
-    <t>0.9848,0.0090,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9931,0.0048,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9656,0.0474,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.8081,0.0170,0.2665,0.0004</t>
-  </si>
-  <si>
-    <t>0.2923,0.0087,0.8686,0.0003</t>
-  </si>
-  <si>
-    <t>0.8833,0.0076,0.2225,0.0012</t>
-  </si>
-  <si>
-    <t>0.1101,0.3982,0.6678,0.0002</t>
-  </si>
-  <si>
-    <t>0.4065,0.0099,0.7863,0.0005</t>
-  </si>
-  <si>
-    <t>0.9451,0.0902,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.2332,0.8702,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.9877,0.0083,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9732,0.0363,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.4230,0.2089,0.2068,0.0005</t>
-  </si>
-  <si>
-    <t>0.7990,0.0349,0.1652,0.0005</t>
-  </si>
-  <si>
-    <t>0.9562,0.0122,0.0272,0.0001</t>
-  </si>
-  <si>
-    <t>0.4431,0.3792,0.0304,0.0001</t>
-  </si>
-  <si>
-    <t>0.2177,0.0899,0.7092,0.0001</t>
-  </si>
-  <si>
-    <t>0.9677,0.0096,0.0120,0.0020</t>
-  </si>
-  <si>
-    <t>0.9789,0.0071,0.0009,0.0017</t>
-  </si>
-  <si>
-    <t>0.9665,0.0101,0.0042,0.0041</t>
-  </si>
-  <si>
-    <t>0.9381,0.0226,0.0113,0.0058</t>
-  </si>
-  <si>
-    <t>0.9105,0.0601,0.0181,0.0040</t>
-  </si>
-  <si>
-    <t>0.9213,0.0711,0.0097,0.0007</t>
-  </si>
-  <si>
-    <t>0.6799,0.1101,0.2210,0.0009</t>
-  </si>
-  <si>
-    <t>0.7142,0.0058,0.4002,0.0002</t>
-  </si>
-  <si>
-    <t>0.5653,0.0308,0.3819,0.0009</t>
-  </si>
-  <si>
-    <t>0.7425,0.0080,0.4953,0.0002</t>
-  </si>
-  <si>
-    <t>0.9134,0.0202,0.0631,0.0002</t>
-  </si>
-  <si>
-    <t>0.8972,0.0261,0.0269,0.0000</t>
-  </si>
-  <si>
-    <t>0.9317,0.0643,0.0030,0.0013</t>
-  </si>
-  <si>
-    <t>0.9086,0.1296,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.9288,0.0704,0.0041,0.0013</t>
-  </si>
-  <si>
-    <t>0.8524,0.1834,0.0148,0.0009</t>
-  </si>
-  <si>
-    <t>0.9862,0.0130,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.8934,0.1371,0.0043,0.0008</t>
-  </si>
-  <si>
-    <t>0.9629,0.0501,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.6118,0.5112,0.0118,0.0011</t>
-  </si>
-  <si>
-    <t>0.9657,0.0328,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.9609,0.0402,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.9520,0.0472,0.0016,0.0006</t>
-  </si>
-  <si>
-    <t>0.9672,0.0398,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9664,0.0374,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9773,0.0226,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9740,0.0349,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.8179,0.2234,0.0085,0.0019</t>
-  </si>
-  <si>
-    <t>0.0921,0.0273,0.9410,0.0003</t>
-  </si>
-  <si>
-    <t>0.9814,0.0016,0.0251,0.0002</t>
-  </si>
-  <si>
-    <t>0.9535,0.0115,0.0354,0.0006</t>
-  </si>
-  <si>
-    <t>0.9762,0.0048,0.0156,0.0006</t>
-  </si>
-  <si>
-    <t>0.7820,0.3435,0.0051,0.0003</t>
-  </si>
-  <si>
-    <t>0.8333,0.2793,0.0053,0.0002</t>
-  </si>
-  <si>
-    <t>0.7737,0.4024,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.6837,0.4865,0.0136,0.0004</t>
-  </si>
-  <si>
-    <t>0.6582,0.5379,0.0044,0.0002</t>
-  </si>
-  <si>
-    <t>0.0387,0.9719,0.0140,0.0001</t>
-  </si>
-  <si>
-    <t>0.9119,0.1280,0.0063,0.0009</t>
-  </si>
-  <si>
-    <t>0.9668,0.0323,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.9830,0.0046,0.0119,0.0002</t>
-  </si>
-  <si>
-    <t>0.9851,0.0037,0.0062,0.0002</t>
-  </si>
-  <si>
-    <t>0.8829,0.0499,0.0653,0.0025</t>
-  </si>
-  <si>
-    <t>0.9831,0.0062,0.0045,0.0002</t>
-  </si>
-  <si>
-    <t>0.9900,0.0080,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.9481,0.0922,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.8905,0.1528,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.5804,0.0271,0.2284,0.0002</t>
-  </si>
-  <si>
-    <t>0.8539,0.1852,0.0061,0.0001</t>
-  </si>
-  <si>
-    <t>0.8795,0.1743,0.0049,0.0005</t>
-  </si>
-  <si>
-    <t>0.8365,0.2378,0.0109,0.0007</t>
-  </si>
-  <si>
-    <t>0.9307,0.0945,0.0042,0.0005</t>
-  </si>
-  <si>
-    <t>0.9349,0.0686,0.0020,0.0012</t>
-  </si>
-  <si>
-    <t>0.9254,0.0862,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.8400,0.1974,0.0082,0.0006</t>
-  </si>
-  <si>
-    <t>0.9742,0.0217,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.9742,0.0243,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.8597,0.1991,0.0062,0.0005</t>
-  </si>
-  <si>
-    <t>0.8476,0.1696,0.0125,0.0016</t>
-  </si>
-  <si>
-    <t>0.9894,0.0005,0.0212,0.0001</t>
-  </si>
-  <si>
-    <t>0.9289,0.0122,0.0719,0.0003</t>
-  </si>
-  <si>
-    <t>0.4417,0.0143,0.5341,0.0003</t>
-  </si>
-  <si>
-    <t>0.9583,0.0010,0.0864,0.0001</t>
-  </si>
-  <si>
-    <t>0.9662,0.0350,0.0038,0.0002</t>
-  </si>
-  <si>
-    <t>0.9754,0.0143,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.9372,0.0270,0.0312,0.0006</t>
-  </si>
-  <si>
-    <t>0.9882,0.0036,0.0052,0.0001</t>
-  </si>
-  <si>
-    <t>0.9940,0.0016,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.7936,0.0375,0.0717,0.0639</t>
-  </si>
-  <si>
-    <t>0.9346,0.0097,0.0365,0.0074</t>
-  </si>
-  <si>
-    <t>0.9840,0.0018,0.0016,0.0050</t>
-  </si>
-  <si>
-    <t>0.8934,0.0447,0.0347,0.0003</t>
-  </si>
-  <si>
-    <t>0.9657,0.0256,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.8007,0.2653,0.0085,0.0006</t>
-  </si>
-  <si>
-    <t>0.9513,0.0701,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9332,0.0837,0.0040,0.0004</t>
-  </si>
-  <si>
-    <t>0.9096,0.1178,0.0051,0.0004</t>
-  </si>
-  <si>
-    <t>0.9524,0.0373,0.0063,0.0008</t>
-  </si>
-  <si>
-    <t>0.9214,0.0806,0.0028,0.0009</t>
-  </si>
-  <si>
-    <t>0.5446,0.2046,0.3156,0.0024</t>
-  </si>
-  <si>
-    <t>0.9134,0.0850,0.0083,0.0009</t>
-  </si>
-  <si>
-    <t>0.7864,0.1859,0.0142,0.0051</t>
-  </si>
-  <si>
-    <t>0.8464,0.2126,0.0066,0.0007</t>
-  </si>
-  <si>
-    <t>0.9790,0.0231,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9794,0.0233,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.8154,0.2734,0.0102,0.0002</t>
-  </si>
-  <si>
-    <t>0.9705,0.0302,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9886,0.0142,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9834,0.0226,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9905,0.0087,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9737,0.0214,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.6874,0.4076,0.0141,0.0018</t>
-  </si>
-  <si>
-    <t>0.9679,0.0189,0.0019,0.0017</t>
-  </si>
-  <si>
-    <t>0.7812,0.3296,0.0057,0.0008</t>
-  </si>
-  <si>
-    <t>0.9707,0.0289,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.9345,0.0788,0.0029,0.0007</t>
-  </si>
-  <si>
-    <t>0.9848,0.0119,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.7119,0.4171,0.0116,0.0010</t>
-  </si>
-  <si>
-    <t>0.8718,0.1255,0.0193,0.0012</t>
-  </si>
-  <si>
-    <t>0.5002,0.3201,0.3102,0.0053</t>
-  </si>
-  <si>
-    <t>0.7162,0.4292,0.0094,0.0006</t>
-  </si>
-  <si>
-    <t>0.9803,0.0203,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.6862,0.5180,0.0056,0.0004</t>
-  </si>
-  <si>
-    <t>0.9892,0.0106,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0482,0.2687,0.9363,0.0023</t>
-  </si>
-  <si>
-    <t>0.8835,0.1604,0.0086,0.0005</t>
-  </si>
-  <si>
-    <t>0.8305,0.0058,0.2838,0.0007</t>
-  </si>
-  <si>
-    <t>0.9481,0.0087,0.0563,0.0006</t>
-  </si>
-  <si>
-    <t>0.9748,0.0052,0.0215,0.0007</t>
-  </si>
-  <si>
-    <t>0.1627,0.0207,0.9076,0.0001</t>
-  </si>
-  <si>
-    <t>0.4905,0.0080,0.6360,0.0010</t>
-  </si>
-  <si>
-    <t>0.9294,0.0015,0.1571,0.0002</t>
-  </si>
-  <si>
-    <t>0.9744,0.0076,0.0186,0.0004</t>
-  </si>
-  <si>
-    <t>0.9736,0.0072,0.0204,0.0002</t>
-  </si>
-  <si>
-    <t>0.9825,0.0053,0.0096,0.0002</t>
-  </si>
-  <si>
-    <t>0.9319,0.0511,0.0148,0.0004</t>
-  </si>
-  <si>
-    <t>0.9571,0.0304,0.0090,0.0001</t>
-  </si>
-  <si>
-    <t>0.9475,0.0158,0.0187,0.0011</t>
-  </si>
-  <si>
-    <t>0.9481,0.0310,0.0115,0.0003</t>
-  </si>
-  <si>
-    <t>0.9742,0.0069,0.0223,0.0003</t>
-  </si>
-  <si>
-    <t>0.9543,0.0151,0.0255,0.0006</t>
-  </si>
-  <si>
-    <t>0.9867,0.0125,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9132,0.1581,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.8996,0.2341,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.9574,0.0452,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9799,0.0159,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9930,0.0015,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.9511,0.0245,0.0138,0.0002</t>
-  </si>
-  <si>
-    <t>0.9837,0.0019,0.0108,0.0005</t>
-  </si>
-  <si>
-    <t>0.9837,0.0072,0.0049,0.0002</t>
-  </si>
-  <si>
-    <t>0.9598,0.0203,0.0115,0.0008</t>
-  </si>
-  <si>
-    <t>0.7138,0.0955,0.1601,0.0009</t>
-  </si>
-  <si>
-    <t>0.9862,0.0009,0.0202,0.0001</t>
-  </si>
-  <si>
-    <t>0.9755,0.0025,0.0243,0.0004</t>
-  </si>
-  <si>
-    <t>0.9929,0.0006,0.0110,0.0001</t>
-  </si>
-  <si>
-    <t>0.9465,0.0012,0.1372,0.0001</t>
-  </si>
-  <si>
-    <t>0.9136,0.1076,0.0032,0.0006</t>
-  </si>
-  <si>
-    <t>0.9566,0.0328,0.0016,0.0012</t>
-  </si>
-  <si>
-    <t>0.9509,0.0556,0.0020,0.0008</t>
-  </si>
-  <si>
-    <t>0.8852,0.1281,0.0111,0.0017</t>
-  </si>
-  <si>
-    <t>0.9747,0.0183,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.8894,0.1728,0.0052,0.0004</t>
-  </si>
-  <si>
-    <t>0.9857,0.0107,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.8610,0.1301,0.0061,0.0023</t>
-  </si>
-  <si>
-    <t>0.6440,0.0449,0.2468,0.0004</t>
-  </si>
-  <si>
-    <t>0.9828,0.0075,0.0027,0.0004</t>
-  </si>
-  <si>
-    <t>0.9744,0.0241,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.3087,0.0126,0.8312,0.0003</t>
-  </si>
-  <si>
-    <t>0.0094,0.0057,0.9931,0.0003</t>
-  </si>
-  <si>
-    <t>0.9471,0.0142,0.0473,0.0004</t>
-  </si>
-  <si>
-    <t>0.2592,0.0037,0.8888,0.0005</t>
-  </si>
-  <si>
-    <t>0.6367,0.2351,0.0250,0.0003</t>
-  </si>
-  <si>
-    <t>0.0097,0.0148,0.9835,0.0019</t>
-  </si>
-  <si>
-    <t>0.9751,0.0016,0.0535,0.0003</t>
-  </si>
-  <si>
-    <t>0.9363,0.0215,0.0285,0.0004</t>
-  </si>
-  <si>
-    <t>0.9879,0.0026,0.0068,0.0003</t>
-  </si>
-  <si>
-    <t>0.9810,0.0038,0.0135,0.0003</t>
-  </si>
-  <si>
-    <t>0.9590,0.0144,0.0184,0.0005</t>
-  </si>
-  <si>
-    <t>0.7800,0.3530,0.0060,0.0005</t>
-  </si>
-  <si>
-    <t>0.8914,0.1213,0.0044,0.0014</t>
-  </si>
-  <si>
-    <t>0.9636,0.0341,0.0016,0.0010</t>
-  </si>
-  <si>
-    <t>0.9501,0.0635,0.0024,0.0007</t>
-  </si>
-  <si>
-    <t>0.9802,0.0196,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9657,0.0333,0.0020,0.0007</t>
-  </si>
-  <si>
-    <t>0.9630,0.0384,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.9354,0.0524,0.0027,0.0017</t>
-  </si>
-  <si>
-    <t>0.9510,0.0056,0.0590,0.0002</t>
-  </si>
-  <si>
-    <t>0.8250,0.0031,0.3462,0.0007</t>
-  </si>
-  <si>
-    <t>0.1046,0.0238,0.8837,0.0033</t>
-  </si>
-  <si>
-    <t>0.9780,0.0034,0.0241,0.0003</t>
-  </si>
-  <si>
-    <t>0.8426,0.0042,0.2334,0.0002</t>
-  </si>
-  <si>
-    <t>0.8354,0.0133,0.2111,0.0009</t>
-  </si>
-  <si>
-    <t>0.7953,0.0140,0.2902,0.0014</t>
-  </si>
-  <si>
-    <t>0.9099,0.0084,0.0886,0.0008</t>
-  </si>
-  <si>
-    <t>0.9913,0.0023,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9506,0.0232,0.0132,0.0019</t>
-  </si>
-  <si>
-    <t>0.9842,0.0031,0.0035,0.0018</t>
-  </si>
-  <si>
-    <t>0.9650,0.0138,0.0045,0.0040</t>
-  </si>
-  <si>
-    <t>0.9593,0.0085,0.0047,0.0074</t>
-  </si>
-  <si>
-    <t>0.9802,0.0156,0.0018,0.0002</t>
+    <t>0.9534,0.0110,0.0167,0.0066</t>
+  </si>
+  <si>
+    <t>0.0539,0.0008,0.0006,0.9855</t>
+  </si>
+  <si>
+    <t>0.9767,0.0013,0.0001,0.0072</t>
+  </si>
+  <si>
+    <t>0.2055,0.0048,0.0015,0.9124</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0008,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9974,0.0027,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9946,0.0058,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0009,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9625,0.0046,0.0366,0.0004</t>
+  </si>
+  <si>
+    <t>0.2480,0.0097,0.8690,0.0025</t>
+  </si>
+  <si>
+    <t>0.2541,0.0109,0.8500,0.0001</t>
+  </si>
+  <si>
+    <t>0.2860,0.0367,0.7011,0.0155</t>
+  </si>
+  <si>
+    <t>0.9480,0.0112,0.0450,0.0005</t>
+  </si>
+  <si>
+    <t>0.0016,0.9980,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0194,0.9744,0.0058,0.0060</t>
+  </si>
+  <si>
+    <t>0.0556,0.9413,0.0248,0.0022</t>
+  </si>
+  <si>
+    <t>0.0305,0.9736,0.0100,0.0010</t>
+  </si>
+  <si>
+    <t>0.0028,0.9945,0.0054,0.0004</t>
+  </si>
+  <si>
+    <t>0.7314,0.0101,0.2489,0.0343</t>
+  </si>
+  <si>
+    <t>0.4211,0.0206,0.5705,0.0278</t>
+  </si>
+  <si>
+    <t>0.0115,0.0045,0.9893,0.0006</t>
+  </si>
+  <si>
+    <t>0.0724,0.0235,0.9073,0.0013</t>
+  </si>
+  <si>
+    <t>0.0593,0.0056,0.9571,0.0016</t>
+  </si>
+  <si>
+    <t>0.1264,0.0025,0.9459,0.0003</t>
+  </si>
+  <si>
+    <t>0.0026,0.0005,0.9962,0.0006</t>
+  </si>
+  <si>
+    <t>0.5128,0.6316,0.0141,0.0027</t>
+  </si>
+  <si>
+    <t>0.5855,0.4699,0.0930,0.0080</t>
+  </si>
+  <si>
+    <t>0.0066,0.0048,0.9943,0.0003</t>
+  </si>
+  <si>
+    <t>0.0027,0.9804,0.1568,0.0000</t>
+  </si>
+  <si>
+    <t>0.9136,0.0568,0.0415,0.0086</t>
+  </si>
+  <si>
+    <t>0.5075,0.4642,0.0811,0.0037</t>
+  </si>
+  <si>
+    <t>0.9282,0.1169,0.0059,0.0002</t>
+  </si>
+  <si>
+    <t>0.0092,0.9856,0.0473,0.0002</t>
+  </si>
+  <si>
+    <t>0.0304,0.0746,0.9144,0.0044</t>
+  </si>
+  <si>
+    <t>0.4755,0.0007,0.6384,0.0029</t>
+  </si>
+  <si>
+    <t>0.1136,0.0378,0.8975,0.0027</t>
+  </si>
+  <si>
+    <t>0.0558,0.0005,0.9551,0.0020</t>
+  </si>
+  <si>
+    <t>0.0099,0.0949,0.9824,0.0005</t>
+  </si>
+  <si>
+    <t>0.0224,0.5933,0.3282,0.0014</t>
+  </si>
+  <si>
+    <t>0.0141,0.0058,0.9838,0.0015</t>
+  </si>
+  <si>
+    <t>0.7622,0.2095,0.0072,0.0253</t>
+  </si>
+  <si>
+    <t>0.0019,0.9950,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.0074,0.9749,0.0432,0.0015</t>
+  </si>
+  <si>
+    <t>0.0092,0.9823,0.0207,0.0007</t>
+  </si>
+  <si>
+    <t>0.0007,0.0232,0.9947,0.0030</t>
+  </si>
+  <si>
+    <t>0.0015,0.0736,0.9917,0.0004</t>
+  </si>
+  <si>
+    <t>0.0617,0.0068,0.9542,0.0022</t>
+  </si>
+  <si>
+    <t>0.1484,0.0053,0.9340,0.0004</t>
+  </si>
+  <si>
+    <t>0.0042,0.0060,0.9962,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.0086,0.9956,0.0008</t>
+  </si>
+  <si>
+    <t>0.9925,0.0092,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9799,0.0247,0.0026,0.0003</t>
+  </si>
+  <si>
+    <t>0.9957,0.0020,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.0207,0.0549,0.9881,0.0004</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0054,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9639,0.9751,0.0005</t>
+  </si>
+  <si>
+    <t>0.0013,0.0010,0.9981,0.0006</t>
+  </si>
+  <si>
+    <t>0.0039,0.1279,0.9920,0.0011</t>
+  </si>
+  <si>
+    <t>0.0016,0.9315,0.9661,0.0005</t>
+  </si>
+  <si>
+    <t>0.0020,0.0049,0.9964,0.0007</t>
+  </si>
+  <si>
+    <t>0.0229,0.9732,0.0290,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.9957,0.0043,0.0001</t>
+  </si>
+  <si>
+    <t>0.9719,0.0083,0.0266,0.0005</t>
+  </si>
+  <si>
+    <t>0.0686,0.0435,0.9365,0.0014</t>
+  </si>
+  <si>
+    <t>0.0142,0.0647,0.9844,0.0020</t>
+  </si>
+  <si>
+    <t>0.0001,0.9815,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.0182,0.3413,0.9017,0.0006</t>
+  </si>
+  <si>
+    <t>0.0016,0.9934,0.0162,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.9801,0.9583,0.0001</t>
+  </si>
+  <si>
+    <t>0.0066,0.0002,0.0023,0.9947</t>
+  </si>
+  <si>
+    <t>0.0010,0.0010,0.0003,0.9991</t>
+  </si>
+  <si>
+    <t>0.0393,0.0007,0.0001,0.9919</t>
+  </si>
+  <si>
+    <t>0.0172,0.0036,0.0031,0.9899</t>
+  </si>
+  <si>
+    <t>0.0470,0.0005,0.0015,0.9845</t>
+  </si>
+  <si>
+    <t>0.0068,0.0029,0.0009,0.9959</t>
+  </si>
+  <si>
+    <t>0.0007,0.9817,0.9558,0.0004</t>
+  </si>
+  <si>
+    <t>0.0046,0.1553,0.9834,0.0006</t>
+  </si>
+  <si>
+    <t>0.0174,0.3201,0.7285,0.0023</t>
+  </si>
+  <si>
+    <t>0.0012,0.8200,0.9892,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.9703,0.8505,0.0002</t>
+  </si>
+  <si>
+    <t>0.0048,0.9321,0.2488,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0014,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9528,0.1118,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9576,0.0984,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0012,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0008,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0048,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9979,0.0028,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0024,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0137,0.0088,0.9910,0.0003</t>
+  </si>
+  <si>
+    <t>0.0122,0.0081,0.9893,0.0016</t>
+  </si>
+  <si>
+    <t>0.9480,0.0030,0.0661,0.0027</t>
+  </si>
+  <si>
+    <t>0.0210,0.0020,0.9853,0.0006</t>
+  </si>
+  <si>
+    <t>0.0235,0.9826,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.9987,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.9950,0.0027,0.0007</t>
+  </si>
+  <si>
+    <t>0.0102,0.9839,0.0048,0.0020</t>
+  </si>
+  <si>
+    <t>0.0030,0.9943,0.0025,0.0002</t>
+  </si>
+  <si>
+    <t>0.0022,0.9967,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.1079,0.9363,0.0037,0.0009</t>
+  </si>
+  <si>
+    <t>0.8557,0.0317,0.1486,0.0043</t>
+  </si>
+  <si>
+    <t>0.1952,0.0030,0.8991,0.0008</t>
+  </si>
+  <si>
+    <t>0.5006,0.0164,0.5379,0.0232</t>
+  </si>
+  <si>
+    <t>0.1429,0.0224,0.8566,0.0157</t>
+  </si>
+  <si>
+    <t>0.0634,0.3374,0.1246,0.8114</t>
+  </si>
+  <si>
+    <t>0.0044,0.9933,0.0027,0.0003</t>
+  </si>
+  <si>
+    <t>0.0046,0.9824,0.0176,0.0065</t>
+  </si>
+  <si>
+    <t>0.0049,0.9912,0.0045,0.0004</t>
+  </si>
+  <si>
+    <t>0.0013,0.8063,0.9582,0.0010</t>
+  </si>
+  <si>
+    <t>0.0162,0.9862,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.8758,0.2172,0.0070,0.0011</t>
+  </si>
+  <si>
+    <t>0.7340,0.4288,0.0074,0.0005</t>
+  </si>
+  <si>
+    <t>0.9960,0.0016,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9966,0.0020,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9940,0.0022,0.0026,0.0005</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9964,0.0007,0.0034,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9963,0.0020,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.2667,0.9905,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.8981,0.9922,0.0001</t>
+  </si>
+  <si>
+    <t>0.0061,0.0598,0.9675,0.0045</t>
+  </si>
+  <si>
+    <t>0.0134,0.0897,0.9530,0.0018</t>
+  </si>
+  <si>
+    <t>0.9823,0.0027,0.0096,0.0019</t>
+  </si>
+  <si>
+    <t>0.9708,0.0018,0.0213,0.0022</t>
+  </si>
+  <si>
+    <t>0.1565,0.0044,0.8890,0.0041</t>
+  </si>
+  <si>
+    <t>0.7711,0.0206,0.2503,0.0064</t>
+  </si>
+  <si>
+    <t>0.2550,0.0002,0.0005,0.9534</t>
+  </si>
+  <si>
+    <t>0.0004,0.0013,0.0028,0.9983</t>
+  </si>
+  <si>
+    <t>0.0034,0.0051,0.0017,0.9965</t>
+  </si>
+  <si>
+    <t>0.0267,0.0001,0.0005,0.9928</t>
+  </si>
+  <si>
+    <t>0.0007,0.9928,0.4122,0.0005</t>
+  </si>
+  <si>
+    <t>0.9974,0.0009,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0299,0.9668,0.0029,0.0062</t>
+  </si>
+  <si>
+    <t>0.9931,0.0036,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.8232,0.3669,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.9921,0.0004,0.0012,0.0033</t>
+  </si>
+  <si>
+    <t>0.9339,0.0126,0.0066,0.0350</t>
+  </si>
+  <si>
+    <t>0.9967,0.0016,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.0110,0.0324,0.9532,0.0703</t>
+  </si>
+  <si>
+    <t>0.9738,0.0023,0.0024,0.0183</t>
+  </si>
+  <si>
+    <t>0.9946,0.0003,0.0012,0.0021</t>
+  </si>
+  <si>
+    <t>0.1372,0.8898,0.0170,0.0051</t>
+  </si>
+  <si>
+    <t>0.9721,0.0208,0.0069,0.0008</t>
+  </si>
+  <si>
+    <t>0.9749,0.0119,0.0135,0.0010</t>
+  </si>
+  <si>
+    <t>0.6112,0.2957,0.1188,0.0146</t>
+  </si>
+  <si>
+    <t>0.5894,0.5901,0.0026,0.0021</t>
+  </si>
+  <si>
+    <t>0.9864,0.0091,0.0024,0.0005</t>
+  </si>
+  <si>
+    <t>0.9969,0.0026,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0011,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9962,0.0023,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9974,0.0007,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9965,0.0018,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9975,0.0005,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9553,0.0642,0.0019,0.0009</t>
+  </si>
+  <si>
+    <t>0.4291,0.7239,0.0056,0.0005</t>
+  </si>
+  <si>
+    <t>0.8923,0.1917,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.0021,0.8241,0.9909,0.0004</t>
+  </si>
+  <si>
+    <t>0.9908,0.0098,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9657,0.0144,0.0118,0.0034</t>
+  </si>
+  <si>
+    <t>0.9987,0.0010,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.2352,0.9036,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.0068,0.9987,0.0004</t>
+  </si>
+  <si>
+    <t>0.9068,0.0430,0.0716,0.0017</t>
+  </si>
+  <si>
+    <t>0.0014,0.0008,0.9966,0.0007</t>
+  </si>
+  <si>
+    <t>0.0018,0.0317,0.9964,0.0010</t>
+  </si>
+  <si>
+    <t>0.1291,0.0041,0.9296,0.0009</t>
+  </si>
+  <si>
+    <t>0.0104,0.1006,0.9916,0.0003</t>
+  </si>
+  <si>
+    <t>0.0090,0.0105,0.9899,0.0010</t>
+  </si>
+  <si>
+    <t>0.0007,0.0013,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.0050,0.9947,0.0015</t>
+  </si>
+  <si>
+    <t>0.0276,0.0294,0.9281,0.0235</t>
+  </si>
+  <si>
+    <t>0.3398,0.0223,0.7839,0.0028</t>
+  </si>
+  <si>
+    <t>0.7524,0.0627,0.1914,0.0152</t>
+  </si>
+  <si>
+    <t>0.0229,0.0267,0.9645,0.0004</t>
+  </si>
+  <si>
+    <t>0.0088,0.9456,0.0632,0.0017</t>
+  </si>
+  <si>
+    <t>0.8546,0.0205,0.0787,0.0003</t>
+  </si>
+  <si>
+    <t>0.7181,0.0281,0.3090,0.0056</t>
+  </si>
+  <si>
+    <t>0.0275,0.2092,0.8024,0.0218</t>
+  </si>
+  <si>
+    <t>0.2054,0.9173,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.0077,0.9921,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.9735,0.0853,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.7607,0.4156,0.0063,0.0005</t>
+  </si>
+  <si>
+    <t>0.8366,0.4260,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.6079,0.2536,0.0967,0.0050</t>
+  </si>
+  <si>
+    <t>0.9021,0.0089,0.1064,0.0046</t>
+  </si>
+  <si>
+    <t>0.9365,0.0122,0.0132,0.0145</t>
+  </si>
+  <si>
+    <t>0.9109,0.0234,0.0891,0.0040</t>
+  </si>
+  <si>
+    <t>0.0261,0.0188,0.9654,0.0053</t>
+  </si>
+  <si>
+    <t>0.0016,0.0024,0.9956,0.0025</t>
+  </si>
+  <si>
+    <t>0.0041,0.0249,0.9874,0.0020</t>
+  </si>
+  <si>
+    <t>0.0463,0.0082,0.9636,0.0018</t>
+  </si>
+  <si>
+    <t>0.0056,0.1470,0.9832,0.0010</t>
+  </si>
+  <si>
+    <t>0.0541,0.1575,0.8244,0.0070</t>
+  </si>
+  <si>
+    <t>0.9984,0.0005,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0010,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9935,0.0041,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.9975,0.0020,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9851,0.0145,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9936,0.0079,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0028,0.0254,0.9963,0.0006</t>
+  </si>
+  <si>
+    <t>0.0492,0.9146,0.0877,0.0039</t>
+  </si>
+  <si>
+    <t>0.9765,0.0031,0.0231,0.0007</t>
+  </si>
+  <si>
+    <t>0.0026,0.0086,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0082,0.9954,0.0012</t>
+  </si>
+  <si>
+    <t>0.0006,0.1536,0.9967,0.0004</t>
+  </si>
+  <si>
+    <t>0.0024,0.0039,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0078,0.0040,0.9828,0.0025</t>
+  </si>
+  <si>
+    <t>0.0053,0.0273,0.9897,0.0015</t>
+  </si>
+  <si>
+    <t>0.0120,0.0118,0.9821,0.0017</t>
+  </si>
+  <si>
+    <t>0.0124,0.0137,0.9761,0.0020</t>
+  </si>
+  <si>
+    <t>0.8395,0.0123,0.1654,0.0115</t>
+  </si>
+  <si>
+    <t>0.5205,0.0018,0.6691,0.0021</t>
+  </si>
+  <si>
+    <t>0.9760,0.0034,0.0196,0.0011</t>
+  </si>
+  <si>
+    <t>0.9947,0.0080,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0020,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9883,0.0225,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9929,0.0076,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0021,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0103,0.4014,0.9106,0.0016</t>
+  </si>
+  <si>
+    <t>0.0026,0.0238,0.9938,0.0007</t>
+  </si>
+  <si>
+    <t>0.0028,0.0303,0.9884,0.0014</t>
+  </si>
+  <si>
+    <t>0.0419,0.0076,0.9679,0.0005</t>
+  </si>
+  <si>
+    <t>0.0049,0.0002,0.9963,0.0002</t>
+  </si>
+  <si>
+    <t>0.0595,0.0065,0.9379,0.0095</t>
+  </si>
+  <si>
+    <t>0.0251,0.0178,0.9528,0.0113</t>
+  </si>
+  <si>
+    <t>0.0141,0.0050,0.9808,0.0024</t>
+  </si>
+  <si>
+    <t>0.9549,0.0008,0.0040,0.0405</t>
+  </si>
+  <si>
+    <t>0.0331,0.0013,0.0235,0.9609</t>
+  </si>
+  <si>
+    <t>0.1515,0.0020,0.0005,0.9557</t>
+  </si>
+  <si>
+    <t>0.0047,0.0002,0.0010,0.9974</t>
+  </si>
+  <si>
+    <t>0.0043,0.0009,0.0017,0.9969</t>
+  </si>
+  <si>
+    <t>0.9903,0.0007,0.0061,0.0007</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2387,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
         <v>295</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3269,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D96" t="s">
         <v>358</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3577,7 +3577,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
         <v>380</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4207,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
         <v>425</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4431,7 +4431,7 @@
         <v>259</v>
       </c>
       <c r="C179" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D179" t="s">
         <v>441</v>
@@ -4445,7 +4445,7 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D180" t="s">
         <v>442</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4823,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
         <v>469</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5187,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
         <v>495</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
